--- a/assets/xlsx/Testing LGI 1.xlsx
+++ b/assets/xlsx/Testing LGI 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BMG\Documents\GITHUB\automationtestingjudges\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F6F7B8-47A1-4C4E-9011-690AB0BB237F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFE4325-89F5-492F-9986-768E472AC9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="204">
   <si>
     <t>No</t>
   </si>
@@ -1053,7 +1053,7 @@
   <cols>
     <col min="1" max="1" width="9.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.54296875" customWidth="1"/>
+    <col min="3" max="3" width="163.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="115.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1085,7 +1085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" ht="75.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1095,9 +1095,11 @@
       <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="75.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1107,9 +1109,11 @@
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="75.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1119,7 +1123,9 @@
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="38" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
